--- a/erp-server/erp-server-plm/src/main/resources/excel/productCertificateError.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productCertificateError.xlsx
@@ -137,7 +137,7 @@
     <t>{.dictProjectName}</t>
   </si>
   <si>
-    <t>{.pathUrl}</t>
+    <t>{.attachName}</t>
   </si>
   <si>
     <t>{.certificateValidTime}</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productCertificateError.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productCertificateError.xlsx
@@ -137,7 +137,7 @@
     <t>{.dictProjectName}</t>
   </si>
   <si>
-    <t>{.attachName}</t>
+    <t>{.pathUrl}</t>
   </si>
   <si>
     <t>{.certificateValidTime}</t>
